--- a/customer_satisfaction_evaluation_forms/029_product_review_submission_feedback_form--customer_satisfaction_evaluation_forms.xlsx
+++ b/customer_satisfaction_evaluation_forms/029_product_review_submission_feedback_form--customer_satisfaction_evaluation_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -711,8 +711,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="44" customWidth="1" min="2" max="2"/>
-    <col width="44" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -740,12 +740,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_6,_'name':_'rating_1',_'label':_1}</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 6, 'name': 'rating_1', 'label': 1}</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -757,12 +757,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_7,_'name':_'rating_2',_'label':_2}</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 7, 'name': 'rating_2', 'label': 2}</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -774,12 +774,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_8,_'name':_'rating_3',_'label':_3}</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 8, 'name': 'rating_3', 'label': 3}</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -791,12 +791,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_9,_'name':_'rating_4',_'label':_4}</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 9, 'name': 'rating_4', 'label': 4}</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -808,12 +808,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_10,_'name':_'rating_5',_'label':_5}</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 10, 'name': 'rating_5', 'label': 5}</t>
+          <t>5</t>
         </is>
       </c>
     </row>
